--- a/Hummus_Fit_Crate_Build_Sheet.xlsx
+++ b/Hummus_Fit_Crate_Build_Sheet.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,12 +67,6 @@
       <color rgb="00E8612C"/>
       <sz val="10.5"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00767c85"/>
-      <sz val="10.5"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -118,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -141,10 +135,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -738,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -815,7 +808,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Strawberry Crunch Milkshake</t>
+          <t>Buffin Muffin - Apple Pie-Ceps</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -827,11 +820,11 @@
         <v>6</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>139</v>
+        <v>368.5</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -856,7 +849,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Buff Roll</t>
+          <t>Buffin Muffin - Apple Pie-Ceps</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -865,19 +858,19 @@
         </is>
       </c>
       <c r="F3" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>112</v>
+        <v>368.5</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -897,7 +890,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Strawberry Crunch Milkshake</t>
+          <t>Buffin Muffin - Apple Pie-Ceps</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -909,11 +902,11 @@
         <v>6</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>139</v>
+        <v>368.5</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -938,7 +931,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Banana Cream Protein Dream</t>
+          <t>Buffin Muffin - Banana Choc. Chip</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -950,16 +943,16 @@
         <v>4</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>73</v>
+        <v>164.1</v>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -979,7 +972,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - ChocoLIT</t>
+          <t>Buffin Muffin - Banana Choc. Chip</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -988,19 +981,19 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>72</v>
+        <v>164.1</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1013,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - TwistBar</t>
+          <t>Buffin Muffin - Banana Cream Protein Dream</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1029,19 +1022,19 @@
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>74</v>
+        <v>237.7</v>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1054,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Cookie Butter Tres Leches</t>
+          <t>Buffin Muffin - Banana Cream Protein Dream</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1070,19 +1063,19 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>59</v>
+        <v>237.7</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1095,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Apple Pie-Ceps</t>
+          <t>Buffin Muffin - Blueberry</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -1111,19 +1104,19 @@
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>103</v>
+        <v>146.2</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1136,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Buffcoff</t>
+          <t>Buffin Muffin - Blueberry</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1152,19 +1145,19 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>60</v>
+        <v>146.2</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1177,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Strawberry Buff Blast</t>
+          <t>Buffin Muffin - Boston Chocolate Creme</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1193,19 +1186,19 @@
         </is>
       </c>
       <c r="F11" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>82</v>
+        <v>210.2</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1218,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Blueberry</t>
+          <t>Buffin Muffin - Boston Chocolate Creme</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1234,19 +1227,19 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>58</v>
+        <v>210.2</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1259,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Buff Served</t>
+          <t>Buffin Muffin - Buff Roll</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1275,19 +1268,19 @@
         </is>
       </c>
       <c r="F13" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>66</v>
+        <v>307.1</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1300,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Cinna Blast</t>
+          <t>Buffin Muffin - Buff Roll</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1316,19 +1309,19 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>44</v>
+        <v>307.1</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1341,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Boston Chocolate Creme</t>
+          <t>Buffin Muffin - Buff Roll</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1357,19 +1350,19 @@
         </is>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>47</v>
+        <v>307.1</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1382,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - German Chocolate Cake</t>
+          <t>Buffin Muffin - Buff Served</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1398,19 +1391,19 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>54</v>
+        <v>140.1</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1423,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Welcome to the Sno</t>
+          <t>Buffin Muffin - Buffcoff</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1439,19 +1432,19 @@
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>27</v>
+        <v>203.4</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1464,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Double Chocolate Brownie</t>
+          <t>Buffin Muffin - Buffcoff</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1480,19 +1473,19 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>53</v>
+        <v>203.4</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1512,28 +1505,28 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Overnight Oats - Chocolate Peanut Butter</t>
+          <t>Buffin Muffin - ChocoLIT</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>12</v>
+        <v>235.9</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1553,28 +1546,28 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Overnight Oats - Blueberry Muffin</t>
+          <t>Buffin Muffin - ChocoLIT</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>24</v>
+        <v>235.9</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1587,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Banana Choc. Chip</t>
+          <t>Buffin Muffin - Cinna Blast</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1603,19 +1596,19 @@
         </is>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>33</v>
+        <v>217.1</v>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1628,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Gluten Free Cookies and Milk</t>
+          <t>Buffin Muffin - Cinna Blast</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1644,19 +1637,19 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>32</v>
+        <v>217.1</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1676,28 +1669,28 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Peanut Butter Chocolate Gree-Yo</t>
+          <t>Buffin Muffin - Cookie Butter Tres Leches</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>27.8876</v>
+        <v>222.9</v>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1717,28 +1710,28 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Buff Crisp Bar - Cinna Crunch</t>
+          <t>Buffin Muffin - Cookie Butter Tres Leches</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>20.82343333333333</v>
+        <v>222.9</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1758,28 +1751,28 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Protein Chocolate Pudding</t>
+          <t>Buffin Muffin - Cookies and Cream Crunch</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>19.9469</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 7-day avg -- no 90d history, likely new item)</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1799,28 +1792,28 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Buff Crisp Bar - Original Recipe</t>
+          <t>Buffin Muffin - Double Chocolate Brownie</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>15.31626666666667</v>
+        <v>231.4</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1840,28 +1833,28 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>S'Mores Gree-Yo</t>
+          <t>Buffin Muffin - Double Chocolate Brownie</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>14.65886666666667</v>
+        <v>231.4</v>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1874,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Cookies and Cream Crunch</t>
+          <t>Buffin Muffin - German Chocolate Cake</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1890,304 +1883,304 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12.0062</v>
+        <v>195.6</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>K2-01</t>
+          <t>K1-28</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Buff Crisp Bar - Fruity Cereal</t>
+          <t>Buffin Muffin - German Chocolate Cake</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>11.75246666666667</v>
+        <v>195.6</v>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>K2-02</t>
+          <t>K1-29</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Overnight Oats - Cookie Creme</t>
+          <t>Buffin Muffin - Gluten Free Confetti Pop</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>10</v>
+        <v>50.5</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>K2-03</t>
+          <t>K1-30</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Overnight Oats - Peanut Butter &amp; Jelly</t>
+          <t>Buffin Muffin - Gluten Free Cookies and Milk</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>K2-04</t>
+          <t>K1-31</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Buffin Muffin - Gluten Free Cookies and Milk</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Muffin</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Overnight Oats - Fitella</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Oats</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="G32" s="6" t="n">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>K2-05</t>
+          <t>K1-32</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Overnight Oats - Peanut Butter Brownie</t>
+          <t>Buffin Muffin - Strawberry Buff Blast</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F33" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>8</v>
+        <v>285.2</v>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>K2-06</t>
+          <t>K1-33</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Overnight Oats - Graham Fetti</t>
+          <t>Buffin Muffin - Strawberry Buff Blast</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>6</v>
+        <v>285.2</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>K2-07</t>
+          <t>K1-34</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Overnight Oats - Cookie Dough</t>
+          <t>Buffin Muffin - Strawberry Crunch Milkshake</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F35" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
         </is>
@@ -2196,48 +2189,48 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>K2-08</t>
+          <t>K1-35</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Overnight Oats - Toast n' Crunch</t>
+          <t>Buffin Muffin - TwistBar</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>3</v>
+        <v>284.6</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>K2-09</t>
+          <t>K2-01</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -2246,11 +2239,11 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Buffin Muffin - Gluten Free Confetti Pop</t>
+          <t>Buffin Muffin - TwistBar</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -2259,26 +2252,26 @@
         </is>
       </c>
       <c r="F37" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>8</v>
+        <v>284.6</v>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>K2-10</t>
+          <t>K2-02</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2287,39 +2280,39 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Overnight Oats - Dubai Chocolate</t>
+          <t>Buffin Muffin - Welcome to the Sno</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Muffin</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>4</v>
+        <v>120.2</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>K2-11</t>
+          <t>K2-03</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -2328,39 +2321,39 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Overnight Oats - Cannoli</t>
+          <t>3 Banana Chocolate Protein Poppers</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Oats</t>
+          <t>Snack</t>
         </is>
       </c>
       <c r="F39" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>7.179499999999999</v>
+        <v>73</v>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>K2-12</t>
+          <t>K2-04</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2369,39 +2362,39 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Buff Crisp Bar - Chocolate</t>
+          <t>Overnight Oats - Banana Chocolate Chip</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Oats</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>4.7056</v>
+        <v>34.2</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>K2-13</t>
+          <t>K2-05</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -2410,11 +2403,11 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Overnight Oats - Banana Chocolate Chip</t>
+          <t>Overnight Oats - Blueberry Muffin</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -2423,26 +2416,26 @@
         </is>
       </c>
       <c r="F41" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>4</v>
+        <v>50.1</v>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>K2-14</t>
+          <t>K2-06</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -2451,39 +2444,39 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Peanut Butter Energy Bites</t>
+          <t>Overnight Oats - Cannoli</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Snack</t>
+          <t>Oats</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4</v>
+        <v>25.9</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>K2-15</t>
+          <t>K2-07</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -2492,11 +2485,11 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>3 Banana Chocolate Protein Poppers</t>
+          <t>Buff Crisp Bar - Chocolate</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -2508,57 +2501,877 @@
         <v>1</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>3</v>
+        <v>20.3</v>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>K2-08</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Chocolate Peanut Butter</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>K2-09</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Buff Crisp Bar - Cinna Crunch</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>K2-10</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Cookie Creme</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>K2-11</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Cookie Dough</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>K2-12</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Cookies and Cream Crunch</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>336</v>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 7-day avg only -- launched within the last week, no longer history yet)</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>K2-13</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Cookies and Cream Crunch</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>336</v>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 7-day avg only -- launched within the last week, no longer history yet)</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>K2-14</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Cookies and Cream Crunch</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>336</v>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 7-day avg only -- launched within the last week, no longer history yet)</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>K2-15</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Cookies and Cream Crunch - Exclusive- 20</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 30-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
           <t>K2-16</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>K2</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C52" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Overnight Oats - Cookies n Cream</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Oats</t>
         </is>
       </c>
-      <c r="F44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="6" t="n">
+      <c r="F52" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+      <c r="G52" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>K2-17</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Dubai Chocolate</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>K2-18</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Fitella</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>K2-19</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Buff Crisp Bar - Fruity Cereal</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>K2-20</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Graham Fetti</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>K2-21</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Buff Crisp Bar - Original Recipe</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>K2-22</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Peanut Butter &amp; Jelly</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>K2-23</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Peanut Butter Brownie</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>K2-24</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Peanut Butter Chocolate Gree-Yo</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>K2-25</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Peanut Butter Energy Bites</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>K2-26</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Protein Chocolate Pudding</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>K2-27</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>S'Mores Gree-Yo</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>K2-28</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Overnight Oats - Toast n' Crunch</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -2573,7 +3386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2650,7 +3463,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>BBQ Chicken Garlic Parm Potatoes</t>
+          <t>6-Guys Patty Melt</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -2659,19 +3472,19 @@
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>83</v>
+        <v>100.5</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -2691,7 +3504,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Closed on Sunday Crispy Chicken Bowl</t>
+          <t>Arnold 2022 Bowl</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -2700,19 +3513,19 @@
         </is>
       </c>
       <c r="F3" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>81</v>
+        <v>106.7</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -2732,7 +3545,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Texas Queso Steak Bowl</t>
+          <t>Baja Chicken Tacos</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -2741,14 +3554,14 @@
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>59</v>
+        <v>163.7</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -2773,7 +3586,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Farfalle &amp; Chicken Alfredo</t>
+          <t>Baked Herbed Tilapia (1lb Competition Approved)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -2782,19 +3595,19 @@
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>61</v>
+        <v>9.9</v>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -2814,7 +3627,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Rigatoni &amp; Meatballs</t>
+          <t>BBQ Chicken Garlic Parm Potatoes</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2823,19 +3636,19 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>31</v>
+        <v>237.2</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -2855,7 +3668,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Meatball Parmesan Wrap</t>
+          <t>BBQ Chicken Garlic Parm Potatoes</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -2864,19 +3677,19 @@
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>34</v>
+        <v>237.2</v>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -2896,7 +3709,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Grilled Chicken Parmesan Wrap</t>
+          <t>BBQ Chicken Mac Bowl</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2905,19 +3718,19 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>40</v>
+        <v>112.1</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -2937,7 +3750,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Spicy Buffalo Wrap</t>
+          <t>BBQ Meltdown</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -2946,19 +3759,19 @@
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>53</v>
+        <v>89.5</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -2978,7 +3791,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Broritto Burrito</t>
+          <t>Blueberry French Toast</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2990,16 +3803,16 @@
         <v>3</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>71</v>
+        <v>60.3</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3832,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>HFit Signature Fold</t>
+          <t>Breakfast Burrito</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -3028,19 +3841,19 @@
         </is>
       </c>
       <c r="F11" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>60</v>
+        <v>89.5</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3873,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Strongsville Chicken Ranch Fold</t>
+          <t>Brookfield Chicken Bowl</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3069,19 +3882,19 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>45</v>
+        <v>126.3</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3914,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Crispy Baked Chicken Wrap</t>
+          <t>Broritto Burrito</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -3110,19 +3923,19 @@
         </is>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>46</v>
+        <v>275.6</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3955,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Buffalo Chicken Quesadilla</t>
+          <t>Broritto Burrito</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3151,19 +3964,19 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>60</v>
+        <v>275.6</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3996,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Taco Build Quesadilla</t>
+          <t>Buffalo Chicken Meatballs</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -3192,19 +4005,19 @@
         </is>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>55</v>
+        <v>105.8</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3224,7 +4037,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Hey Arnold! Burrito</t>
+          <t>Buffalo Chicken Quesadilla</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -3233,19 +4046,19 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>49</v>
+        <v>123.2</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3265,7 +4078,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Fit-Fil-A</t>
+          <t>Buffalo Crispy Chicken Wrap</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -3274,19 +4087,19 @@
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>43</v>
+        <v>120.4</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3306,7 +4119,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>BBQ Chicken Mac Bowl</t>
+          <t>Buffalo Mac N Chicken</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -3315,19 +4128,19 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>48</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3347,7 +4160,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Lo Mein Teriyaki Steak</t>
+          <t>Low Carb Keto Cheeseburger Bowl</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -3356,19 +4169,19 @@
         </is>
       </c>
       <c r="F19" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>42</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3388,7 +4201,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Herb Butter Steak Tips Bowl</t>
+          <t>Cheeseburger Bowl</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -3397,19 +4210,19 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>54</v>
+        <v>174.4</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg) - backfilled: product was live and selling in Shopify but was missing from the original catalog pull</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3429,7 +4242,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>GLORIOUS GAINS Steak Bites &amp; Cilantro Lime Rice</t>
+          <t>Cheeseburger Bowl</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -3438,19 +4251,19 @@
         </is>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>32</v>
+        <v>174.4</v>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg) - backfilled: product was live and selling in Shopify but was missing from the original catalog pull</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3470,7 +4283,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>BBQ Meltdown</t>
+          <t>Chicken Mushroom Pot Stickers</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3479,19 +4292,19 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>35</v>
+        <v>57.7</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3511,7 +4324,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Zeus Bowl</t>
+          <t>Chicken Stir Fry</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -3520,19 +4333,19 @@
         </is>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>34</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3552,7 +4365,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Baja Chicken Tacos</t>
+          <t>Chicken Taco Bowl</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -3561,19 +4374,19 @@
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>70</v>
+        <v>120.2</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3593,7 +4406,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Stacked and Jacked</t>
+          <t>Chipotle Chicken (1lb Competition Approved)</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3602,19 +4415,19 @@
         </is>
       </c>
       <c r="F25" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>41</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3634,7 +4447,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Philly Cheesesteak Quesadilla</t>
+          <t>Cinnamon Roll Pancakes</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3643,14 +4456,14 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>48</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -3675,7 +4488,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Brookfield Chicken Bowl</t>
+          <t>Closed on Sunday Crispy Chicken Bowl</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -3684,19 +4497,19 @@
         </is>
       </c>
       <c r="F27" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>32</v>
+        <v>112.3</v>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
@@ -3716,7 +4529,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Buffalo Mac N Chicken</t>
+          <t>Club Wrap</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3725,39 +4538,39 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>33</v>
+        <v>99.5</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>M2-01</t>
+          <t>M1-28</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>6-Guys Patty Melt</t>
+          <t>Competition Approved 90/10 Lean Ground Beef (1lb)</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -3769,23 +4582,23 @@
         <v>2</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>30</v>
+        <v>28.7</v>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>M2-02</t>
+          <t>M2-01</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -3794,11 +4607,11 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Southwest Chicken Quesadilla</t>
+          <t>Competition Approved Baked Sweet Potato Fries (1lb)</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -3810,23 +4623,23 @@
         <v>2</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>28</v>
+        <v>38.8</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>M2-03</t>
+          <t>M2-02</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3835,11 +4648,11 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Grilled Chicken Pesto Wrap</t>
+          <t>Competition Approved Chicken Kebab (1lb)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -3848,26 +4661,26 @@
         </is>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>M2-04</t>
+          <t>M2-03</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3876,11 +4689,11 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Nacho Average Bowl</t>
+          <t>Competition Approved Grilled Chicken (1lb)</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3889,26 +4702,26 @@
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>30</v>
+        <v>108.1</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>M2-05</t>
+          <t>M2-04</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3917,11 +4730,11 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Zeus Bowl V2</t>
+          <t>Competition Approved Grilled Chicken W/ Smokin Poppie Sauce (1lb)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -3930,26 +4743,26 @@
         </is>
       </c>
       <c r="F33" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>24</v>
+        <v>63.9</v>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>M2-06</t>
+          <t>M2-05</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3958,11 +4771,11 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Chicken Taco Bowl</t>
+          <t>Competition Approved Grilled Flank Steak (1lb)</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -3974,23 +4787,23 @@
         <v>2</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>29</v>
+        <v>46.4</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>M2-07</t>
+          <t>M2-06</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -3999,11 +4812,11 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Chicken Stir Fry</t>
+          <t>Competition Approved Lemon Pepper Salmon (1lb)</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -4015,23 +4828,23 @@
         <v>1</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>M2-08</t>
+          <t>M2-07</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -4040,11 +4853,11 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Teriyaki Flank Bowl</t>
+          <t>Competition Approved Oven Baked Cod (1lb)</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -4053,26 +4866,26 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>M2-09</t>
+          <t>M2-08</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4081,11 +4894,11 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Hot Honey Steak &amp; Mac</t>
+          <t>Competition Approved Sticky Rice (1lb)</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -4097,23 +4910,23 @@
         <v>2</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>28</v>
+        <v>33.3</v>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>M2-10</t>
+          <t>M2-09</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -4122,11 +4935,11 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>MsWendy Buff Nuggets</t>
+          <t>Competition Approved White Basmati Rice (1lb)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -4138,23 +4951,23 @@
         <v>1</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>M2-11</t>
+          <t>M2-10</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -4163,11 +4976,11 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Gluten Free Carbonara Chicken</t>
+          <t>Crispy Baked Chicken Wrap</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -4176,26 +4989,26 @@
         </is>
       </c>
       <c r="F39" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>24</v>
+        <v>191.8</v>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>M2-12</t>
+          <t>M2-11</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -4204,11 +5017,11 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Arnold 2022 Bowl</t>
+          <t>Crispy Baked Chicken Wrap</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -4217,26 +5030,26 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>19</v>
+        <v>191.8</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>M2-13</t>
+          <t>M2-12</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -4245,11 +5058,11 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Club Wrap</t>
+          <t>Crispy Vegan Wrap</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -4261,23 +5074,23 @@
         <v>1</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>M2-14</t>
+          <t>M2-13</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4286,11 +5099,11 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>The Arches Mac Daddy Wrap</t>
+          <t>Farfalle &amp; Chicken Alfredo</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -4299,26 +5112,26 @@
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>21</v>
+        <v>110.5</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>M2-15</t>
+          <t>M2-14</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -4327,11 +5140,11 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Low Carb Keto Cheeseburger Bowl</t>
+          <t>Fit Ala Vodka With Chicken</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -4340,26 +5153,26 @@
         </is>
       </c>
       <c r="F43" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>21</v>
+        <v>98.5</v>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>M2-16</t>
+          <t>M2-15</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4368,11 +5181,11 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>TexMex Potato Hash</t>
+          <t>Fit-Fil-A</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -4381,26 +5194,26 @@
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>26</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>M2-17</t>
+          <t>M2-16</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -4409,11 +5222,11 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Chicken Mushroom Pot Stickers</t>
+          <t>GLORIOUS GAINS Steak Bites &amp; Cilantro Lime Rice</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -4422,26 +5235,26 @@
         </is>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>23</v>
+        <v>110.8</v>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>M2-18</t>
+          <t>M2-17</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4450,11 +5263,11 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>The Clean Bulk Pasta Bowl</t>
+          <t>Gluten Free Carbonara Chicken</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -4463,26 +5276,26 @@
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>24</v>
+        <v>78.8</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>M2-19</t>
+          <t>M2-18</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -4491,11 +5304,11 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Breakfast Burrito</t>
+          <t>Grilled Chicken Parmesan Wrap</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -4504,26 +5317,26 @@
         </is>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>21</v>
+        <v>122.8</v>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>M2-20</t>
+          <t>M2-19</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4532,11 +5345,11 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Buffalo Chicken Meatballs</t>
+          <t>Grilled Chicken Pesto Wrap</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -4545,26 +5358,26 @@
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>19</v>
+        <v>111.3</v>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>M2-21</t>
+          <t>M2-20</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -4573,11 +5386,11 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Southwest Chicken Bowl</t>
+          <t>Herb Butter Steak Tips Bowl</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -4586,26 +5399,26 @@
         </is>
       </c>
       <c r="F49" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>20</v>
+        <v>156.2</v>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>M2-22</t>
+          <t>M2-21</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4614,11 +5427,11 @@
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Strawberry Protein French Toast</t>
+          <t>Hey Arnold! Burrito</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -4627,26 +5440,26 @@
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>28</v>
+        <v>118.3</v>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>M2-23</t>
+          <t>M2-22</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -4655,11 +5468,11 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Chipotle Chicken (1lb Competition Approved)</t>
+          <t>HFit Signature Fold</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -4668,26 +5481,26 @@
         </is>
       </c>
       <c r="F51" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>19</v>
+        <v>120.3</v>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>M2-24</t>
+          <t>M2-23</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -4696,11 +5509,11 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Competition Approved Grilled Chicken (1lb)</t>
+          <t>Honey Garlic Crispy Chicken Tacos</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -4712,23 +5525,23 @@
         <v>1</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>no recent Shopify sales (Online Store) -- floor 1 crate</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>M2-25</t>
+          <t>M2-24</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -4737,11 +5550,11 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Competition Approved Grilled Flank Steak (1lb)</t>
+          <t>Hot Honey Steak &amp; Mac</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -4750,26 +5563,26 @@
         </is>
       </c>
       <c r="F53" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>16</v>
+        <v>90.5</v>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>M2-26</t>
+          <t>M2-25</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -4778,11 +5591,11 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fit Ala Vodka With Chicken</t>
+          <t>Keto Ricotta Meatballs</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -4791,26 +5604,26 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>23.91436666666666</v>
+        <v>86.3</v>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>M2-27</t>
+          <t>M2-26</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -4819,11 +5632,11 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Blueberry French Toast</t>
+          <t>Lo Mein Teriyaki Steak</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -4832,39 +5645,39 @@
         </is>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>15.23553333333333</v>
+        <v>118.8</v>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I55" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>M3-01</t>
+          <t>M2-27</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Keto Ricotta Meatballs</t>
+          <t>Meatball Parmesan Wrap</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -4873,39 +5686,39 @@
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>15</v>
+        <v>115.6</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>M3-02</t>
+          <t>M2-28</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Soho Steak Bowl</t>
+          <t>MsWendy Buff Nuggets</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -4914,26 +5727,26 @@
         </is>
       </c>
       <c r="F57" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>15</v>
+        <v>88.8</v>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>M3-03</t>
+          <t>M3-01</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -4942,39 +5755,39 @@
         </is>
       </c>
       <c r="C58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Nacho Average Bowl</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Thai Chili Chicken</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Meal</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="G58" s="6" t="n">
-        <v>9</v>
+        <v>67.8</v>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>M3-04</t>
+          <t>M3-02</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -4983,11 +5796,11 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Competition Approved Grilled Chicken W/ Smokin Poppie Sauce (1lb)</t>
+          <t>Nacho Average Vegan Bowl</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -4999,23 +5812,23 @@
         <v>1</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>M3-05</t>
+          <t>M3-03</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -5024,7 +5837,7 @@
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
@@ -5037,26 +5850,26 @@
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>8</v>
+        <v>65.7</v>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>M3-06</t>
+          <t>M3-04</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -5065,11 +5878,11 @@
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Cinnamon Roll Pancakes</t>
+          <t>Philly Cheesesteak Quesadilla</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -5081,14 +5894,14 @@
         <v>1</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
         </is>
@@ -5097,7 +5910,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>M3-07</t>
+          <t>M3-05</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -5106,11 +5919,11 @@
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Competition Approved Chicken Kebab (1lb)</t>
+          <t>Pineapple Teriyaki Meatballs</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -5119,26 +5932,26 @@
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>13</v>
+        <v>57.6</v>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>M3-08</t>
+          <t>M3-06</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -5147,11 +5960,11 @@
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Buffalo Crispy Chicken Wrap</t>
+          <t>Rigatoni &amp; Meatballs</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -5160,26 +5973,26 @@
         </is>
       </c>
       <c r="F63" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>11</v>
+        <v>113.2</v>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>M3-09</t>
+          <t>M3-07</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -5188,11 +6001,11 @@
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Competition Approved 90/10 Lean Ground Beef (1lb)</t>
+          <t>Soho Steak Bowl</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -5201,26 +6014,26 @@
         </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>9</v>
+        <v>88.8</v>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>M3-10</t>
+          <t>M3-08</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -5229,11 +6042,11 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Competition Approved Sticky Rice (1lb)</t>
+          <t>Southwest Chicken Bowl</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -5242,26 +6055,26 @@
         </is>
       </c>
       <c r="F65" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>8.949866666666667</v>
+        <v>112.5</v>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I65" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>M3-11</t>
+          <t>M3-09</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -5270,11 +6083,11 @@
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Competition Approved Oven Baked Cod (1lb)</t>
+          <t>Southwest Chicken Quesadilla</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -5283,26 +6096,26 @@
         </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>8</v>
+        <v>88.5</v>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>M3-12</t>
+          <t>M3-10</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -5311,11 +6124,11 @@
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Competition Approved White Basmati Rice (1lb)</t>
+          <t>Spicy Buffalo Wrap</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -5324,26 +6137,26 @@
         </is>
       </c>
       <c r="F67" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>5</v>
+        <v>150.5</v>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>M3-13</t>
+          <t>M3-11</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -5352,11 +6165,11 @@
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Pineapple Teriyaki Meatballs</t>
+          <t>Stacked and Jacked</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -5365,26 +6178,26 @@
         </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>7</v>
+        <v>116.1</v>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>M3-14</t>
+          <t>M3-12</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -5393,11 +6206,11 @@
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Baked Herbed Tilapia (1lb Competition Approved)</t>
+          <t>Strawberry Protein French Toast</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -5406,26 +6219,26 @@
         </is>
       </c>
       <c r="F69" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>2</v>
+        <v>61.9</v>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>M3-15</t>
+          <t>M3-13</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -5434,11 +6247,11 @@
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Competition Approved Baked Sweet Potato Fries (1lb)</t>
+          <t>Strongsville Chicken Ranch Fold</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -5447,26 +6260,26 @@
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>4</v>
+        <v>112.4</v>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>M3-16</t>
+          <t>M3-14</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -5475,11 +6288,11 @@
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Competition Approved Lemon Pepper Salmon (1lb)</t>
+          <t>Taco Build Quesadilla</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -5488,26 +6301,26 @@
         </is>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>3</v>
+        <v>127.6</v>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>M3-17</t>
+          <t>M3-15</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -5516,11 +6329,11 @@
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Nacho Average Vegan Bowl</t>
+          <t>Teriyaki Flank Bowl</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -5529,26 +6342,26 @@
         </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>3.212033333333333</v>
+        <v>105.2</v>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>M3-18</t>
+          <t>M3-16</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -5557,11 +6370,11 @@
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Turkey Bacon Cheddar Egg Muffins</t>
+          <t>Texas Queso Steak Bowl</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -5570,17 +6383,17 @@
         </is>
       </c>
       <c r="F73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3</v>
+        <v>31.9</v>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I73" s="10" t="inlineStr">
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
         </is>
@@ -5589,7 +6402,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>M3-19</t>
+          <t>M3-17</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -5598,11 +6411,11 @@
         </is>
       </c>
       <c r="C74" s="5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Crispy Vegan Wrap</t>
+          <t>TexMex Potato Hash</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -5611,26 +6424,26 @@
         </is>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>2.323966666666667</v>
+        <v>104.5</v>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>M3-20</t>
+          <t>M3-18</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
@@ -5639,11 +6452,11 @@
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Vegan Breakfast Sandwich</t>
+          <t>Thai Chili Chicken</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -5652,26 +6465,26 @@
         </is>
       </c>
       <c r="F75" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>2.3182</v>
+        <v>126.7</v>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>M3-21</t>
+          <t>M3-19</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -5680,11 +6493,11 @@
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Vegan Cheeseburger Bowl</t>
+          <t>The Arches Mac Daddy Wrap</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -5693,26 +6506,26 @@
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>2</v>
+        <v>36.7</v>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>M3-22</t>
+          <t>M3-20</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
@@ -5721,11 +6534,11 @@
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Vegan Chorizo Quesadilla</t>
+          <t>The Clean Bulk Pasta Bowl</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -5734,26 +6547,26 @@
         </is>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1</v>
+        <v>81.3</v>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>real</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>CHECK — real vs blended diverge &gt;2.5x, single-day sample</t>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>M3-23</t>
+          <t>M3-21</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -5762,11 +6575,11 @@
         </is>
       </c>
       <c r="C78" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Honey Garlic Crispy Chicken Tacos</t>
+          <t>Turkey Bacon Cheddar Egg Muffins</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -5775,26 +6588,26 @@
         </is>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>M3-24</t>
+          <t>M3-22</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -5803,11 +6616,11 @@
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>West Coast Secret Sauce Bowl</t>
+          <t>Vegan Breakfast Sandwich</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -5819,16 +6632,221 @@
         <v>1</v>
       </c>
       <c r="G79" s="9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>M3-23</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Vegan Cheeseburger Bowl</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>M3-24</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Vegan Chorizo Quesadilla</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>M3-25</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>West Coast Secret Sauce Bowl</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>blended x0.173 correction (no real-order match)</t>
-        </is>
-      </c>
-      <c r="I79" s="12" t="inlineStr">
-        <is>
-          <t>Fallback — no real-order match</t>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>no recent Shopify sales (Online Store) -- floor 1 crate</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>M3-26</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Zeus Bowl</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G83" s="9" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>M3-27</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Zeus Bowl V2</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>real (Shopify Online Store, 90-day trailing avg)</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>Good — real order data</t>
         </is>
       </c>
     </row>
